--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99252</v>
+        <v>99258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110324</v>
+        <v>110330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99258</v>
+        <v>99260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110330</v>
+        <v>110332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99260</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110332</v>
+        <v>110333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99267</v>
+        <v>99271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110339</v>
+        <v>110343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110343</v>
+        <v>110345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99273</v>
+        <v>99275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110345</v>
+        <v>110347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99275</v>
+        <v>99288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110347</v>
+        <v>110360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99288</v>
+        <v>99290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110360</v>
+        <v>110362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99290</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110362</v>
+        <v>110367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110367</v>
+        <v>110389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99303</v>
+        <v>99304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110389</v>
+        <v>110390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99304</v>
+        <v>99309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110390</v>
+        <v>110395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110395</v>
+        <v>110398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110398</v>
+        <v>110404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110404</v>
+        <v>110405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99317</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110405</v>
+        <v>110417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110417</v>
+        <v>110418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99330</v>
+        <v>99333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110418</v>
+        <v>110421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99333</v>
+        <v>99334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29970-2026 artfynd.xlsx
+++ b/artfynd/A 29970-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951533</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136951534</v>
       </c>
       <c r="B3" t="n">
-        <v>99334</v>
+        <v>99337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136956990</v>
       </c>
       <c r="B4" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136956991</v>
       </c>
       <c r="B5" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
